--- a/pandas/customers_clean.xlsx
+++ b/pandas/customers_clean.xlsx
@@ -2025,7 +2025,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Saudi Arabia </t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="H30" s="1" t="n">
